--- a/output/daily_ratings/uk_ratings_2026-05-27.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-05-27.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,18 +524,18 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tricky Jenny</t>
+          <t>Lairy Mary</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -544,14 +544,16 @@
       <c r="M2" t="n">
         <v>62.33</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -580,28 +582,30 @@
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lairy Mary</t>
+          <t>Tree Wizard</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M3" t="n">
         <v>62.33</v>
       </c>
       <c r="N3" t="n">
-        <v>72.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -638,30 +642,30 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tree Wizard</t>
+          <t>Penny Arcade (IRE)</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>62.33</v>
       </c>
       <c r="N4" t="n">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,30 +702,30 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Penny Arcade (IRE)</t>
+          <t>Spirit Of Mary</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>4.25</v>
       </c>
       <c r="M5" t="n">
         <v>62.33</v>
       </c>
       <c r="N5" t="n">
-        <v>71.5</v>
+        <v>53.9</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -758,30 +762,30 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Spirit Of Mary</t>
+          <t>Jimmy You Mushroom (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4.25</v>
+        <v>9.25</v>
       </c>
       <c r="M6" t="n">
         <v>62.33</v>
       </c>
       <c r="N6" t="n">
-        <v>53.9</v>
+        <v>44.8</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -818,30 +822,30 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jimmy You Mushroom (IRE)</t>
+          <t>Spark In The Coal (IRE)</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>62.33</v>
       </c>
       <c r="N7" t="n">
-        <v>44.8</v>
+        <v>30.3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -849,7 +853,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -878,30 +882,30 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Spark In The Coal (IRE)</t>
+          <t>Toon Army (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>62.33</v>
       </c>
       <c r="N8" t="n">
-        <v>30.3</v>
+        <v>32.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -909,7 +913,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -937,40 +941,24 @@
       <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Toon Army (IRE)</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>123</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12</v>
-      </c>
-      <c r="M9" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="N9" t="n">
-        <v>32.5</v>
-      </c>
+          <t>Tricky Jenny</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1027,7 +1015,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -1087,7 +1075,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="12">
@@ -1147,7 +1135,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1187,7 +1175,7 @@
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1199,7 +1187,7 @@
         <v>94.45999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>46.8</v>
+        <v>42.7</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1207,7 +1195,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1476,34 +1464,36 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tropez Power (IRE)</t>
+          <t>This Farh</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K18" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>90.59</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>81.2</v>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1532,34 +1522,38 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Miss Willows</t>
+          <t>Coolree (IRE)</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="K19" t="n">
-        <v>57</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
       <c r="M19" t="n">
         <v>90.59</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>74.3</v>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-12.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
@@ -1588,28 +1582,30 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>This Farh</t>
+          <t>Rajapour (IRE)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" t="n">
-        <v>72</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.05</v>
+      </c>
       <c r="M20" t="n">
         <v>90.59</v>
       </c>
       <c r="N20" t="n">
-        <v>81.2</v>
+        <v>76.2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1617,7 +1613,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1646,30 +1642,30 @@
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Coolree (IRE)</t>
+          <t>Woodstock</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K21" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
         <v>90.59</v>
       </c>
       <c r="N21" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1677,7 +1673,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1706,30 +1702,30 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Rajapour (IRE)</t>
+          <t>Straight A</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K22" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L22" t="n">
-        <v>1.05</v>
+        <v>2.33</v>
       </c>
       <c r="M22" t="n">
         <v>90.59</v>
       </c>
       <c r="N22" t="n">
-        <v>76.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1737,7 +1733,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -1766,30 +1762,30 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Woodstock</t>
+          <t>Harswell Ruby (IRE)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K23" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M23" t="n">
         <v>90.59</v>
       </c>
       <c r="N23" t="n">
-        <v>75.2</v>
+        <v>72.8</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1826,30 +1822,30 @@
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Straight A</t>
+          <t>Sunny Orange (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K24" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L24" t="n">
-        <v>2.33</v>
+        <v>5.88</v>
       </c>
       <c r="M24" t="n">
         <v>90.59</v>
       </c>
       <c r="N24" t="n">
-        <v>71.40000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1857,7 +1853,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
@@ -1886,30 +1882,30 @@
         <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Harswell Ruby (IRE)</t>
+          <t>Judicature</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K25" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
-        <v>2.38</v>
+        <v>8.379999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>90.59</v>
       </c>
       <c r="N25" t="n">
-        <v>72.8</v>
+        <v>55.4</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1917,7 +1913,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1946,30 +1942,30 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sunny Orange (IRE)</t>
+          <t>In A Hurry</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K26" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
-        <v>5.88</v>
+        <v>8.48</v>
       </c>
       <c r="M26" t="n">
         <v>90.59</v>
       </c>
       <c r="N26" t="n">
-        <v>54.4</v>
+        <v>57.9</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1977,7 +1973,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2006,30 +2002,30 @@
         <v>5</v>
       </c>
       <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Yermanthere (IRE)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>8</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Judicature</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>4</v>
-      </c>
       <c r="J27" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K27" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L27" t="n">
-        <v>8.379999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="M27" t="n">
         <v>90.59</v>
       </c>
       <c r="N27" t="n">
-        <v>55.4</v>
+        <v>47.3</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2066,30 +2062,30 @@
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>In A Hurry</t>
+          <t>Thats My Boy Luke</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K28" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L28" t="n">
-        <v>8.48</v>
+        <v>13.23</v>
       </c>
       <c r="M28" t="n">
         <v>90.59</v>
       </c>
       <c r="N28" t="n">
-        <v>57.9</v>
+        <v>40</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2097,7 +2093,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2125,40 +2121,24 @@
       <c r="F29" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Yermanthere (IRE)</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>128</v>
-      </c>
-      <c r="K29" t="n">
-        <v>68</v>
-      </c>
-      <c r="L29" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="M29" t="n">
-        <v>90.59</v>
-      </c>
-      <c r="N29" t="n">
-        <v>53.1</v>
-      </c>
+          <t>Miss Willows</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2185,40 +2165,24 @@
       <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="G30" t="n">
-        <v>11</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Thats My Boy Luke</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>123</v>
-      </c>
-      <c r="K30" t="n">
-        <v>63</v>
-      </c>
-      <c r="L30" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="M30" t="n">
-        <v>90.59</v>
-      </c>
-      <c r="N30" t="n">
-        <v>40</v>
-      </c>
+          <t>Tropez Power (IRE)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2315,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -2327,7 +2291,7 @@
         <v>124.49</v>
       </c>
       <c r="N32" t="n">
-        <v>56.4</v>
+        <v>54.4</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2335,7 +2299,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="33">
@@ -2455,7 +2419,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2515,7 +2479,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2555,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="J36" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K36" t="n">
         <v>75</v>
@@ -2567,7 +2531,7 @@
         <v>124.49</v>
       </c>
       <c r="N36" t="n">
-        <v>45.4</v>
+        <v>42.8</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2575,7 +2539,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2664,34 +2628,36 @@
         <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Beaming Light</t>
+          <t>Penny Ghent</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K38" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>106.03</v>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>57.5</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2720,28 +2686,30 @@
         <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Penny Ghent</t>
+          <t>Princess Vivi</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3</v>
+      </c>
       <c r="M39" t="n">
         <v>106.03</v>
       </c>
       <c r="N39" t="n">
-        <v>57.5</v>
+        <v>49.4</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2749,7 +2717,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="40">
@@ -2778,30 +2746,30 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Princess Vivi</t>
+          <t>Onemorenomore</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K40" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="M40" t="n">
         <v>106.03</v>
       </c>
       <c r="N40" t="n">
-        <v>49.4</v>
+        <v>56.9</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2809,7 +2777,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2838,30 +2806,30 @@
         <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Onemorenomore</t>
+          <t>Poets Dawn</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J41" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K41" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="L41" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="M41" t="n">
         <v>106.03</v>
       </c>
       <c r="N41" t="n">
-        <v>56.9</v>
+        <v>54.1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2869,7 +2837,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2898,30 +2866,30 @@
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Poets Dawn</t>
+          <t>Hostelry</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K42" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L42" t="n">
-        <v>4.75</v>
+        <v>6.75</v>
       </c>
       <c r="M42" t="n">
         <v>106.03</v>
       </c>
       <c r="N42" t="n">
-        <v>58</v>
+        <v>48.2</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2929,7 +2897,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2958,30 +2926,30 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Hostelry</t>
+          <t>Berning Hot (IRE)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K43" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L43" t="n">
-        <v>6.75</v>
+        <v>8.75</v>
       </c>
       <c r="M43" t="n">
         <v>106.03</v>
       </c>
       <c r="N43" t="n">
-        <v>48.2</v>
+        <v>40.1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3018,30 +2986,30 @@
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Berning Hot (IRE)</t>
+          <t>Ring Of Gold</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="K44" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L44" t="n">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="M44" t="n">
         <v>106.03</v>
       </c>
       <c r="N44" t="n">
-        <v>47.2</v>
+        <v>36.2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3077,40 +3045,24 @@
       <c r="F45" t="n">
         <v>6</v>
       </c>
-      <c r="G45" t="n">
-        <v>7</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ring Of Gold</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>9</v>
-      </c>
-      <c r="J45" t="n">
-        <v>122</v>
-      </c>
-      <c r="K45" t="n">
-        <v>47</v>
-      </c>
-      <c r="L45" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="M45" t="n">
-        <v>106.03</v>
-      </c>
-      <c r="N45" t="n">
-        <v>36.2</v>
-      </c>
+          <t>Beaming Light</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3496,34 +3448,36 @@
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cape Sovereign (IRE)</t>
+          <t>King Of The Jungle (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K52" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>60.77</v>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>78.59999999999999</v>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3552,28 +3506,30 @@
         <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>King Of The Jungle (IRE)</t>
+          <t>Crafty Spirit (IRE)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K53" t="n">
-        <v>53</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
       <c r="M53" t="n">
         <v>60.77</v>
       </c>
       <c r="N53" t="n">
-        <v>83.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3581,7 +3537,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
@@ -3610,30 +3566,30 @@
         <v>6</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Crafty Spirit (IRE)</t>
+          <t>South Shore</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="K54" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="M54" t="n">
         <v>60.77</v>
       </c>
       <c r="N54" t="n">
-        <v>70.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3641,7 +3597,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3670,30 +3626,30 @@
         <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>South Shore</t>
+          <t>Thornaby Pearl</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K55" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L55" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="M55" t="n">
         <v>60.77</v>
       </c>
       <c r="N55" t="n">
-        <v>74.8</v>
+        <v>66.5</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3701,7 +3657,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3730,30 +3686,30 @@
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Thornaby Pearl</t>
+          <t>Amerjeet</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K56" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L56" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="M56" t="n">
         <v>60.77</v>
       </c>
       <c r="N56" t="n">
-        <v>68.5</v>
+        <v>58.5</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3761,7 +3717,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
@@ -3790,30 +3746,30 @@
         <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Amerjeet</t>
+          <t>Desert Master</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K57" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L57" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="M57" t="n">
         <v>60.77</v>
       </c>
       <c r="N57" t="n">
-        <v>63.2</v>
+        <v>53</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3821,7 +3777,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
@@ -3850,30 +3806,30 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Desert Master</t>
+          <t>Until Dawn (IRE)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K58" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L58" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="M58" t="n">
         <v>60.77</v>
       </c>
       <c r="N58" t="n">
-        <v>55.1</v>
+        <v>61.1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3881,7 +3837,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3910,30 +3866,30 @@
         <v>6</v>
       </c>
       <c r="G59" t="n">
+        <v>8</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Nordic Glory (IRE)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
         <v>7</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Until Dawn (IRE)</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
       <c r="J59" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K59" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L59" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="M59" t="n">
         <v>60.77</v>
       </c>
       <c r="N59" t="n">
-        <v>62.1</v>
+        <v>51.5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3941,7 +3897,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3970,30 +3926,30 @@
         <v>6</v>
       </c>
       <c r="G60" t="n">
+        <v>9</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>So Grateful</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>8</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Nordic Glory (IRE)</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>7</v>
-      </c>
       <c r="J60" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K60" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L60" t="n">
-        <v>9.25</v>
+        <v>14.75</v>
       </c>
       <c r="M60" t="n">
         <v>60.77</v>
       </c>
       <c r="N60" t="n">
-        <v>58.3</v>
+        <v>32.5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4001,7 +3957,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4029,40 +3985,24 @@
       <c r="F61" t="n">
         <v>6</v>
       </c>
-      <c r="G61" t="n">
-        <v>9</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>So Grateful</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" t="n">
-        <v>128</v>
-      </c>
-      <c r="K61" t="n">
-        <v>53</v>
-      </c>
-      <c r="L61" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="M61" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="N61" t="n">
-        <v>36.5</v>
-      </c>
+          <t>Cape Sovereign (IRE)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4757,7 +4697,7 @@
         <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -4769,7 +4709,7 @@
         <v>114.81</v>
       </c>
       <c r="N73" t="n">
-        <v>48.3</v>
+        <v>44.5</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5344,34 +5284,36 @@
         <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Furhaan</t>
+          <t>Shipshape (IRE)</t>
         </is>
       </c>
       <c r="I83" t="n">
         <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K83" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>168.21</v>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="n">
+        <v>42</v>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="84">
@@ -5400,28 +5342,30 @@
         <v>4</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Shipshape (IRE)</t>
+          <t>Raulin (IRE)</t>
         </is>
       </c>
       <c r="I84" t="n">
         <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K84" t="n">
-        <v>68</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M84" t="n">
         <v>168.21</v>
       </c>
       <c r="N84" t="n">
-        <v>42</v>
+        <v>53.6</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5429,7 +5373,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5458,30 +5402,30 @@
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Raulin (IRE)</t>
+          <t>Ludos Landing (IRE)</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J85" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K85" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L85" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M85" t="n">
         <v>168.21</v>
       </c>
       <c r="N85" t="n">
-        <v>53.6</v>
+        <v>49.7</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5518,30 +5462,30 @@
         <v>4</v>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Ludos Landing (IRE)</t>
+          <t>Gentle Warrior (IRE)</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K86" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L86" t="n">
-        <v>1.78</v>
+        <v>3.28</v>
       </c>
       <c r="M86" t="n">
         <v>168.21</v>
       </c>
       <c r="N86" t="n">
-        <v>49.7</v>
+        <v>45.5</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5577,40 +5521,24 @@
       <c r="F87" t="n">
         <v>4</v>
       </c>
-      <c r="G87" t="n">
-        <v>4</v>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Gentle Warrior (IRE)</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>4</v>
-      </c>
-      <c r="J87" t="n">
-        <v>132</v>
-      </c>
-      <c r="K87" t="n">
-        <v>77</v>
-      </c>
-      <c r="L87" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="M87" t="n">
-        <v>168.21</v>
-      </c>
-      <c r="N87" t="n">
-        <v>45.5</v>
-      </c>
+          <t>Furhaan</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5827,7 +5755,7 @@
         <v>8</v>
       </c>
       <c r="J91" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K91" t="n">
         <v>67</v>
@@ -5839,7 +5767,7 @@
         <v>57.91</v>
       </c>
       <c r="N91" t="n">
-        <v>57.3</v>
+        <v>53.9</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -6543,19 +6471,19 @@
         <v>8</v>
       </c>
       <c r="J103" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K103" t="n">
         <v>67</v>
       </c>
       <c r="L103" t="n">
-        <v>7.95</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="M103" t="n">
         <v>106.63</v>
       </c>
       <c r="N103" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6563,6 +6491,5370 @@
         </is>
       </c>
       <c r="P103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Rhythm N Rock (IRE)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>8</v>
+      </c>
+      <c r="J104" t="n">
+        <v>130</v>
+      </c>
+      <c r="K104" t="n">
+        <v>66</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N104" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Prince Rasam</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>131</v>
+      </c>
+      <c r="K105" t="n">
+        <v>67</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M105" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N105" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Penfolds Grange</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>4</v>
+      </c>
+      <c r="J106" t="n">
+        <v>132</v>
+      </c>
+      <c r="K106" t="n">
+        <v>68</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M106" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N106" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>8</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Valentine Boy</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>137</v>
+      </c>
+      <c r="K107" t="n">
+        <v>68</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M107" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N107" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Forca Timao (IRE)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>6</v>
+      </c>
+      <c r="J108" t="n">
+        <v>127</v>
+      </c>
+      <c r="K108" t="n">
+        <v>61</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M108" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N108" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>U S S Constitution (IRE)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" t="n">
+        <v>130</v>
+      </c>
+      <c r="K109" t="n">
+        <v>61</v>
+      </c>
+      <c r="L109" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M109" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N109" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>8</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>7</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Gunfighter (IRE)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>5</v>
+      </c>
+      <c r="J110" t="n">
+        <v>139</v>
+      </c>
+      <c r="K110" t="n">
+        <v>70</v>
+      </c>
+      <c r="L110" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M110" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N110" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Goldie Trickett (IRE)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>4</v>
+      </c>
+      <c r="J111" t="n">
+        <v>129</v>
+      </c>
+      <c r="K111" t="n">
+        <v>63</v>
+      </c>
+      <c r="L111" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N111" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>8</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>9</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Gennadius</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" t="n">
+        <v>133</v>
+      </c>
+      <c r="K112" t="n">
+        <v>67</v>
+      </c>
+      <c r="L112" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M112" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N112" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>8</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>10</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Darvel (IRE)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>8</v>
+      </c>
+      <c r="J113" t="n">
+        <v>134</v>
+      </c>
+      <c r="K113" t="n">
+        <v>70</v>
+      </c>
+      <c r="L113" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="M113" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N113" t="n">
+        <v>41</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" t="n">
+        <v>11</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kit Gabriel (IRE)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>139</v>
+      </c>
+      <c r="K114" t="n">
+        <v>70</v>
+      </c>
+      <c r="L114" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="M114" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N114" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>5</v>
+      </c>
+      <c r="G115" t="n">
+        <v>12</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Tex (FR)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" t="n">
+        <v>134</v>
+      </c>
+      <c r="K115" t="n">
+        <v>68</v>
+      </c>
+      <c r="L115" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="M115" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N115" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>5</v>
+      </c>
+      <c r="G116" t="n">
+        <v>13</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>136</v>
+      </c>
+      <c r="K116" t="n">
+        <v>70</v>
+      </c>
+      <c r="L116" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N116" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>14</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Shamacid (IRE)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>4</v>
+      </c>
+      <c r="J117" t="n">
+        <v>129</v>
+      </c>
+      <c r="K117" t="n">
+        <v>67</v>
+      </c>
+      <c r="L117" t="n">
+        <v>34.90000000000001</v>
+      </c>
+      <c r="M117" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" t="n">
+        <v>6</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>4</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Moonrise (IRE)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n">
+        <v>128</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="N118" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="n">
+        <v>6</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Eshaa (IRE)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>128</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M119" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="N119" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Phalanx Nation (IRE)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>128</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M120" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="N120" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>4</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Wise And Wonderful</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>128</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>5.279999999999999</v>
+      </c>
+      <c r="M121" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="N121" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="n">
+        <v>6</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>4</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Alice Rocks</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" t="n">
+        <v>128</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>28.28</v>
+      </c>
+      <c r="M122" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Iris Olivia (IRE)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" t="n">
+        <v>7</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Erudition</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>129</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="n">
+        <v>7</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Makerstoun (IRE)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>129</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M125" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N125" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="n">
+        <v>7</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Slalom (IRE)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>129</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M126" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" t="n">
+        <v>7</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Khaleejy (IRE)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>5</v>
+      </c>
+      <c r="J127" t="n">
+        <v>140</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M127" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>3</v>
+      </c>
+      <c r="C128" t="n">
+        <v>7</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Distant Moon (IRE)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>129</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M128" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="n">
+        <v>7</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>4</v>
+      </c>
+      <c r="G129" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Don Pablo Colina</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>129</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M129" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>30</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sahm Naif (IRE)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>129</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="M130" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N130" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>3</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>4</v>
+      </c>
+      <c r="G131" t="n">
+        <v>8</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Mmmbop</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>124</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>9</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Jeans Boy (IRE)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>129</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="M132" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Siddal</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" t="n">
+        <v>124</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M133" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="n">
+        <v>7</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>4</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Masked Warrior</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>133</v>
+      </c>
+      <c r="K134" t="n">
+        <v>81</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N134" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="n">
+        <v>7</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>4</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Tyrant Gg (IRE)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>133</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M135" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="n">
+        <v>7</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>4</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Storming Point</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" t="n">
+        <v>133</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M136" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N136" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>4</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Foxy Night (IRE)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>3</v>
+      </c>
+      <c r="J137" t="n">
+        <v>128</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M137" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N137" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>4</v>
+      </c>
+      <c r="C138" t="n">
+        <v>7</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" t="n">
+        <v>5</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Wintercast</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>133</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="M138" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" t="n">
+        <v>7</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>4</v>
+      </c>
+      <c r="G139" t="n">
+        <v>6</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Conspiracist (FR)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>133</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="M139" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N139" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>4</v>
+      </c>
+      <c r="C140" t="n">
+        <v>7</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>4</v>
+      </c>
+      <c r="G140" t="n">
+        <v>7</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Back At One (IRE)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>133</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M140" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" t="n">
+        <v>7</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>4</v>
+      </c>
+      <c r="G141" t="n">
+        <v>8</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Decalogue (USA)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" t="n">
+        <v>133</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M141" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" t="n">
+        <v>7</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>4</v>
+      </c>
+      <c r="G142" t="n">
+        <v>9</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Olympic Anthem (IRE)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>3</v>
+      </c>
+      <c r="J142" t="n">
+        <v>133</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M142" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>4</v>
+      </c>
+      <c r="C143" t="n">
+        <v>7</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>4</v>
+      </c>
+      <c r="G143" t="n">
+        <v>10</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Hes Perfect (IRE)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>3</v>
+      </c>
+      <c r="J143" t="n">
+        <v>133</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="M143" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>5</v>
+      </c>
+      <c r="C144" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>3</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Water To Wine (FR)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>3</v>
+      </c>
+      <c r="J144" t="n">
+        <v>127</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N144" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>5</v>
+      </c>
+      <c r="C145" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>3</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>White Storm</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>3</v>
+      </c>
+      <c r="J145" t="n">
+        <v>120</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>11</v>
+      </c>
+      <c r="M145" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N145" t="n">
+        <v>33</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>5</v>
+      </c>
+      <c r="C146" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>3</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Tripoli Flyer (IRE)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>135</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M146" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N146" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>3</v>
+      </c>
+      <c r="G147" t="n">
+        <v>4</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Barrister</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>3</v>
+      </c>
+      <c r="J147" t="n">
+        <v>120</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="M147" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N147" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>5</v>
+      </c>
+      <c r="C148" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Take A Chill Pill</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>3</v>
+      </c>
+      <c r="J148" t="n">
+        <v>120</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M148" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N148" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>3</v>
+      </c>
+      <c r="G149" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Flag Of Eva</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>3</v>
+      </c>
+      <c r="J149" t="n">
+        <v>120</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M149" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N149" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>5</v>
+      </c>
+      <c r="C150" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>3</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Noble Grace (IRE)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>5</v>
+      </c>
+      <c r="J150" t="n">
+        <v>130</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="M150" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N150" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>3</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Blue Birdie (IRE)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>3</v>
+      </c>
+      <c r="J151" t="n">
+        <v>115</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="M151" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>3</v>
+      </c>
+      <c r="G152" t="n">
+        <v>9</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Emerald Reine</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>115</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="M152" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sandpyper (IRE)</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>3</v>
+      </c>
+      <c r="J153" t="n">
+        <v>120</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="M153" t="n">
+        <v>140.83</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Surrey King (IRE)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>5</v>
+      </c>
+      <c r="C155" t="n">
+        <v>10.99545454545455</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>3</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Humphrey</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>6</v>
+      </c>
+      <c r="C156" t="n">
+        <v>7</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>4</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Lord Britain</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" t="n">
+        <v>130</v>
+      </c>
+      <c r="K156" t="n">
+        <v>84</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N156" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>6</v>
+      </c>
+      <c r="C157" t="n">
+        <v>7</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>4</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Caviar Cowboy</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>133</v>
+      </c>
+      <c r="K157" t="n">
+        <v>82</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M157" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N157" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>6</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>4</v>
+      </c>
+      <c r="G158" t="n">
+        <v>3</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ya Karim (IRE)</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>3</v>
+      </c>
+      <c r="J158" t="n">
+        <v>134</v>
+      </c>
+      <c r="K158" t="n">
+        <v>83</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M158" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N158" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>6</v>
+      </c>
+      <c r="C159" t="n">
+        <v>7</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>4</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Exotic Baby</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>3</v>
+      </c>
+      <c r="J159" t="n">
+        <v>130</v>
+      </c>
+      <c r="K159" t="n">
+        <v>79</v>
+      </c>
+      <c r="L159" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M159" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N159" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>4</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>On The Inlet (IRE)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>3</v>
+      </c>
+      <c r="J160" t="n">
+        <v>133</v>
+      </c>
+      <c r="K160" t="n">
+        <v>82</v>
+      </c>
+      <c r="L160" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M160" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N160" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" t="n">
+        <v>7</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>4</v>
+      </c>
+      <c r="G161" t="n">
+        <v>6</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kings Trust</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>3</v>
+      </c>
+      <c r="J161" t="n">
+        <v>134</v>
+      </c>
+      <c r="K161" t="n">
+        <v>83</v>
+      </c>
+      <c r="L161" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M161" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N161" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>6</v>
+      </c>
+      <c r="C162" t="n">
+        <v>7</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>4</v>
+      </c>
+      <c r="G162" t="n">
+        <v>7</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Gorey Gold (IRE)</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>3</v>
+      </c>
+      <c r="J162" t="n">
+        <v>132</v>
+      </c>
+      <c r="K162" t="n">
+        <v>81</v>
+      </c>
+      <c r="L162" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M162" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N162" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>7</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>4</v>
+      </c>
+      <c r="G163" t="n">
+        <v>8</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Shahik</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>132</v>
+      </c>
+      <c r="K163" t="n">
+        <v>81</v>
+      </c>
+      <c r="L163" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="M163" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N163" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>6</v>
+      </c>
+      <c r="C164" t="n">
+        <v>7</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>4</v>
+      </c>
+      <c r="G164" t="n">
+        <v>9</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Slight Of Foot</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>3</v>
+      </c>
+      <c r="J164" t="n">
+        <v>128</v>
+      </c>
+      <c r="K164" t="n">
+        <v>77</v>
+      </c>
+      <c r="L164" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="M164" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N164" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>6</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Seu Jo (IRE)</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>3</v>
+      </c>
+      <c r="J165" t="n">
+        <v>130</v>
+      </c>
+      <c r="K165" t="n">
+        <v>79</v>
+      </c>
+      <c r="L165" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M165" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N165" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>6</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>4</v>
+      </c>
+      <c r="G166" t="n">
+        <v>11</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Tamashal (IRE)</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>3</v>
+      </c>
+      <c r="J166" t="n">
+        <v>132</v>
+      </c>
+      <c r="K166" t="n">
+        <v>81</v>
+      </c>
+      <c r="L166" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="M166" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N166" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>4</v>
+      </c>
+      <c r="G167" t="n">
+        <v>12</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Northern Empire (IRE)</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>3</v>
+      </c>
+      <c r="J167" t="n">
+        <v>131</v>
+      </c>
+      <c r="K167" t="n">
+        <v>80</v>
+      </c>
+      <c r="L167" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="M167" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N167" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" t="n">
+        <v>13</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Watcha Snoop (IRE)</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>3</v>
+      </c>
+      <c r="J168" t="n">
+        <v>133</v>
+      </c>
+      <c r="K168" t="n">
+        <v>82</v>
+      </c>
+      <c r="L168" t="n">
+        <v>21</v>
+      </c>
+      <c r="M168" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="N168" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>6</v>
+      </c>
+      <c r="C169" t="n">
+        <v>7</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Ghisa (IRE)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>7</v>
+      </c>
+      <c r="C170" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Ernst Blofeld (IRE)</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>4</v>
+      </c>
+      <c r="J170" t="n">
+        <v>134</v>
+      </c>
+      <c r="K170" t="n">
+        <v>89</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N170" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>7</v>
+      </c>
+      <c r="C171" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>3</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Master Vintner (IRE)</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>4</v>
+      </c>
+      <c r="J171" t="n">
+        <v>132</v>
+      </c>
+      <c r="K171" t="n">
+        <v>87</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M171" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N171" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>7</v>
+      </c>
+      <c r="C172" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Boatswain</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>4</v>
+      </c>
+      <c r="J172" t="n">
+        <v>133</v>
+      </c>
+      <c r="K172" t="n">
+        <v>88</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M172" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N172" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>7</v>
+      </c>
+      <c r="C173" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" t="n">
+        <v>4</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bulletin (IRE)</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>4</v>
+      </c>
+      <c r="J173" t="n">
+        <v>132</v>
+      </c>
+      <c r="K173" t="n">
+        <v>87</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M173" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N173" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>7</v>
+      </c>
+      <c r="C174" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="n">
+        <v>5</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kirchner (IRE)</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>4</v>
+      </c>
+      <c r="J174" t="n">
+        <v>134</v>
+      </c>
+      <c r="K174" t="n">
+        <v>89</v>
+      </c>
+      <c r="L174" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M174" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N174" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>7</v>
+      </c>
+      <c r="C175" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" t="n">
+        <v>6</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Fox Avatar (IRE)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>5</v>
+      </c>
+      <c r="J175" t="n">
+        <v>131</v>
+      </c>
+      <c r="K175" t="n">
+        <v>86</v>
+      </c>
+      <c r="L175" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M175" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N175" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>7</v>
+      </c>
+      <c r="C176" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>3</v>
+      </c>
+      <c r="G176" t="n">
+        <v>7</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Max Mayhem</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>135</v>
+      </c>
+      <c r="K176" t="n">
+        <v>90</v>
+      </c>
+      <c r="L176" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M176" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N176" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>7</v>
+      </c>
+      <c r="C177" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" t="n">
+        <v>8</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Time Loop (IRE)</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>131</v>
+      </c>
+      <c r="K177" t="n">
+        <v>86</v>
+      </c>
+      <c r="L177" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M177" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N177" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G178" t="n">
+        <v>9</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Aqwaam</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>135</v>
+      </c>
+      <c r="K178" t="n">
+        <v>90</v>
+      </c>
+      <c r="L178" t="n">
+        <v>9</v>
+      </c>
+      <c r="M178" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N178" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>7</v>
+      </c>
+      <c r="C179" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>3</v>
+      </c>
+      <c r="G179" t="n">
+        <v>10</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Gentleman Joe</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>134</v>
+      </c>
+      <c r="K179" t="n">
+        <v>89</v>
+      </c>
+      <c r="L179" t="n">
+        <v>34</v>
+      </c>
+      <c r="M179" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N179" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>7</v>
+      </c>
+      <c r="C180" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" t="n">
+        <v>11</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Steel Tiger (IRE)</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>5</v>
+      </c>
+      <c r="J180" t="n">
+        <v>134</v>
+      </c>
+      <c r="K180" t="n">
+        <v>89</v>
+      </c>
+      <c r="L180" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="M180" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N180" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>7</v>
+      </c>
+      <c r="C181" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" t="n">
+        <v>12</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Son Of Man (IRE)</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>5</v>
+      </c>
+      <c r="J181" t="n">
+        <v>130</v>
+      </c>
+      <c r="K181" t="n">
+        <v>85</v>
+      </c>
+      <c r="L181" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="M181" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N181" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>7</v>
+      </c>
+      <c r="C182" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>13</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Miss Tonnerre (IRE)</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>4</v>
+      </c>
+      <c r="J182" t="n">
+        <v>131</v>
+      </c>
+      <c r="K182" t="n">
+        <v>86</v>
+      </c>
+      <c r="L182" t="n">
+        <v>42</v>
+      </c>
+      <c r="M182" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="N182" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>7</v>
+      </c>
+      <c r="C183" t="n">
+        <v>11.99545454545455</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>3</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Alther Walden (HUN)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>8</v>
+      </c>
+      <c r="C184" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>4</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Moon Chime</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>125</v>
+      </c>
+      <c r="K184" t="n">
+        <v>67</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N184" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>8</v>
+      </c>
+      <c r="C185" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>4</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Now The Eagle (FR)</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>119</v>
+      </c>
+      <c r="K185" t="n">
+        <v>67</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M185" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N185" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>8</v>
+      </c>
+      <c r="C186" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>4</v>
+      </c>
+      <c r="G186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Yaa Min</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>4</v>
+      </c>
+      <c r="J186" t="n">
+        <v>136</v>
+      </c>
+      <c r="K186" t="n">
+        <v>79</v>
+      </c>
+      <c r="L186" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M186" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N186" t="n">
+        <v>54</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>8</v>
+      </c>
+      <c r="C187" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>4</v>
+      </c>
+      <c r="G187" t="n">
+        <v>4</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Gooloogong (IRE)</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>6</v>
+      </c>
+      <c r="J187" t="n">
+        <v>133</v>
+      </c>
+      <c r="K187" t="n">
+        <v>75</v>
+      </c>
+      <c r="L187" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M187" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N187" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>8</v>
+      </c>
+      <c r="C188" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>4</v>
+      </c>
+      <c r="G188" t="n">
+        <v>5</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Robusto (IRE)</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>6</v>
+      </c>
+      <c r="J188" t="n">
+        <v>130</v>
+      </c>
+      <c r="K188" t="n">
+        <v>79</v>
+      </c>
+      <c r="L188" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M188" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N188" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>4</v>
+      </c>
+      <c r="G189" t="n">
+        <v>6</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Filibustering</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>5</v>
+      </c>
+      <c r="J189" t="n">
+        <v>133</v>
+      </c>
+      <c r="K189" t="n">
+        <v>75</v>
+      </c>
+      <c r="L189" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M189" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N189" t="n">
+        <v>36</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>8</v>
+      </c>
+      <c r="C190" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>4</v>
+      </c>
+      <c r="G190" t="n">
+        <v>7</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Senor Cortez (IRE)</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>5</v>
+      </c>
+      <c r="J190" t="n">
+        <v>132</v>
+      </c>
+      <c r="K190" t="n">
+        <v>74</v>
+      </c>
+      <c r="L190" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="M190" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N190" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>8</v>
+      </c>
+      <c r="C191" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>4</v>
+      </c>
+      <c r="G191" t="n">
+        <v>8</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Selenic (IRE)</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>4</v>
+      </c>
+      <c r="J191" t="n">
+        <v>133</v>
+      </c>
+      <c r="K191" t="n">
+        <v>76</v>
+      </c>
+      <c r="L191" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="M191" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N191" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>8</v>
+      </c>
+      <c r="C192" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>4</v>
+      </c>
+      <c r="G192" t="n">
+        <v>9</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Premiere Ligne (FR)</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>7</v>
+      </c>
+      <c r="J192" t="n">
+        <v>140</v>
+      </c>
+      <c r="K192" t="n">
+        <v>82</v>
+      </c>
+      <c r="L192" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="M192" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N192" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>8</v>
+      </c>
+      <c r="C193" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>4</v>
+      </c>
+      <c r="G193" t="n">
+        <v>10</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Baltic</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>6</v>
+      </c>
+      <c r="J193" t="n">
+        <v>137</v>
+      </c>
+      <c r="K193" t="n">
+        <v>79</v>
+      </c>
+      <c r="L193" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="M193" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N193" t="n">
+        <v>30</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>KEMPTON PARK</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>8</v>
+      </c>
+      <c r="C194" t="n">
+        <v>15.99090909090909</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Standard To Slow</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>All Weather</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>4</v>
+      </c>
+      <c r="G194" t="n">
+        <v>11</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>High Point (IRE)</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>5</v>
+      </c>
+      <c r="J194" t="n">
+        <v>136</v>
+      </c>
+      <c r="K194" t="n">
+        <v>78</v>
+      </c>
+      <c r="L194" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="M194" t="n">
+        <v>208.14</v>
+      </c>
+      <c r="N194" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
         <v>0</v>
       </c>
     </row>
